--- a/artfynd/A 51047-2025 artfynd.xlsx
+++ b/artfynd/A 51047-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>129000543</v>
       </c>
       <c r="B3" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>129000536</v>
       </c>
       <c r="B4" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>129000537</v>
       </c>
       <c r="B5" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>129000540</v>
       </c>
       <c r="B6" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>129000542</v>
       </c>
       <c r="B7" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>129000541</v>
       </c>
       <c r="B8" t="n">
-        <v>92828</v>
+        <v>92831</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         <v>129000544</v>
       </c>
       <c r="B9" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1529,32 +1529,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129000539</v>
+        <v>129000538</v>
       </c>
       <c r="B10" t="n">
-        <v>92828</v>
+        <v>92813</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>741260</v>
+        <v>741402</v>
       </c>
       <c r="R10" t="n">
-        <v>7294367</v>
+        <v>7294418</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1635,32 +1635,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129000538</v>
+        <v>129000539</v>
       </c>
       <c r="B11" t="n">
-        <v>92810</v>
+        <v>92831</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>741402</v>
+        <v>741260</v>
       </c>
       <c r="R11" t="n">
-        <v>7294418</v>
+        <v>7294367</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 51047-2025 artfynd.xlsx
+++ b/artfynd/A 51047-2025 artfynd.xlsx
@@ -1529,32 +1529,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129000538</v>
+        <v>129000539</v>
       </c>
       <c r="B10" t="n">
-        <v>92813</v>
+        <v>92831</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>741402</v>
+        <v>741260</v>
       </c>
       <c r="R10" t="n">
-        <v>7294418</v>
+        <v>7294367</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1635,32 +1635,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129000539</v>
+        <v>129000538</v>
       </c>
       <c r="B11" t="n">
-        <v>92831</v>
+        <v>92813</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>741260</v>
+        <v>741402</v>
       </c>
       <c r="R11" t="n">
-        <v>7294367</v>
+        <v>7294418</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 51047-2025 artfynd.xlsx
+++ b/artfynd/A 51047-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>129000543</v>
       </c>
       <c r="B3" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>129000536</v>
       </c>
       <c r="B4" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>129000537</v>
       </c>
       <c r="B5" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>129000540</v>
       </c>
       <c r="B6" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>129000542</v>
       </c>
       <c r="B7" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>129000541</v>
       </c>
       <c r="B8" t="n">
-        <v>92831</v>
+        <v>92838</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         <v>129000544</v>
       </c>
       <c r="B9" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>129000539</v>
       </c>
       <c r="B10" t="n">
-        <v>92831</v>
+        <v>92838</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>129000538</v>
       </c>
       <c r="B11" t="n">
-        <v>92813</v>
+        <v>92820</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 51047-2025 artfynd.xlsx
+++ b/artfynd/A 51047-2025 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>129000536</v>
       </c>
       <c r="B4" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>129000537</v>
       </c>
       <c r="B5" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>129000541</v>
       </c>
       <c r="B8" t="n">
-        <v>92838</v>
+        <v>92845</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>129000539</v>
       </c>
       <c r="B10" t="n">
-        <v>92838</v>
+        <v>92845</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>129000538</v>
       </c>
       <c r="B11" t="n">
-        <v>92820</v>
+        <v>92827</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 51047-2025 artfynd.xlsx
+++ b/artfynd/A 51047-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>129000543</v>
       </c>
       <c r="B3" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>129000536</v>
       </c>
       <c r="B4" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>129000537</v>
       </c>
       <c r="B5" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>129000540</v>
       </c>
       <c r="B6" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>129000542</v>
       </c>
       <c r="B7" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>129000541</v>
       </c>
       <c r="B8" t="n">
-        <v>92845</v>
+        <v>92847</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         <v>129000544</v>
       </c>
       <c r="B9" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>129000539</v>
       </c>
       <c r="B10" t="n">
-        <v>92845</v>
+        <v>92847</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>129000538</v>
       </c>
       <c r="B11" t="n">
-        <v>92827</v>
+        <v>92829</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 51047-2025 artfynd.xlsx
+++ b/artfynd/A 51047-2025 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>129000536</v>
       </c>
       <c r="B4" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>129000537</v>
       </c>
       <c r="B5" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>129000541</v>
       </c>
       <c r="B8" t="n">
-        <v>92847</v>
+        <v>92833</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>129000539</v>
       </c>
       <c r="B10" t="n">
-        <v>92847</v>
+        <v>92833</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>129000538</v>
       </c>
       <c r="B11" t="n">
-        <v>92829</v>
+        <v>92815</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 51047-2025 artfynd.xlsx
+++ b/artfynd/A 51047-2025 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>129000536</v>
       </c>
       <c r="B4" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>129000537</v>
       </c>
       <c r="B5" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>129000541</v>
       </c>
       <c r="B8" t="n">
-        <v>92833</v>
+        <v>92834</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>129000539</v>
       </c>
       <c r="B10" t="n">
-        <v>92833</v>
+        <v>92834</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>129000538</v>
       </c>
       <c r="B11" t="n">
-        <v>92815</v>
+        <v>92816</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 51047-2025 artfynd.xlsx
+++ b/artfynd/A 51047-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>129000543</v>
       </c>
       <c r="B3" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>129000536</v>
       </c>
       <c r="B4" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>129000537</v>
       </c>
       <c r="B5" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>129000540</v>
       </c>
       <c r="B6" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>129000542</v>
       </c>
       <c r="B7" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>129000541</v>
       </c>
       <c r="B8" t="n">
-        <v>92834</v>
+        <v>92837</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         <v>129000544</v>
       </c>
       <c r="B9" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>129000539</v>
       </c>
       <c r="B10" t="n">
-        <v>92834</v>
+        <v>92837</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>129000538</v>
       </c>
       <c r="B11" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 51047-2025 artfynd.xlsx
+++ b/artfynd/A 51047-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1739,6 +1739,802 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>131421828</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79282</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Sarvasvägen, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>741410</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7294501</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>131421821</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57896</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Sarvasvägen, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>741194</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7294285</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack färska och gamla, tall</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>131421825</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57896</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Sarvasvägen, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>741401</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7294510</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Nya och gamla ringhack, rikligt, tall.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>131421830</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91846</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Sarvasvägen, Nb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>741165</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7294277</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>131421824</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57896</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Sarvasvägen, Nb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>741275</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7294333</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Gamla och nya ringhack, tallhed.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>131421831</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79258</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Sarvasvägen, Nb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>741264</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7294336</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>131421827</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>639</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Grenlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Evernia mesomorpha</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Nyl.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Sarvasvägen, Nb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>741351</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7294438</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>131421823</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57896</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Sarvasvägen, Nb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>741167</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7294289</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Nya och gamla ringhack rikligt, tall</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51047-2025 artfynd.xlsx
+++ b/artfynd/A 51047-2025 artfynd.xlsx
@@ -2540,7 +2540,7 @@
         <v>132365428</v>
       </c>
       <c r="B20" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         <v>132365365</v>
       </c>
       <c r="B21" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>132365494</v>
       </c>
       <c r="B22" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 51047-2025 artfynd.xlsx
+++ b/artfynd/A 51047-2025 artfynd.xlsx
@@ -2540,7 +2540,7 @@
         <v>132365428</v>
       </c>
       <c r="B20" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         <v>132365365</v>
       </c>
       <c r="B21" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>132365494</v>
       </c>
       <c r="B22" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 51047-2025 artfynd.xlsx
+++ b/artfynd/A 51047-2025 artfynd.xlsx
@@ -2540,7 +2540,7 @@
         <v>132365428</v>
       </c>
       <c r="B20" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         <v>132365365</v>
       </c>
       <c r="B21" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>132365494</v>
       </c>
       <c r="B22" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 51047-2025 artfynd.xlsx
+++ b/artfynd/A 51047-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110044379</v>
+        <v>131421827</v>
       </c>
       <c r="B2" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79442</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>639</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grenlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Evernia mesomorpha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Nyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rävabacken Utv, Nb</t>
+          <t>Sarvasvägen, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>741286.7208872787</v>
+        <v>741351</v>
       </c>
       <c r="R2" t="n">
-        <v>7294516.404592553</v>
+        <v>7294438</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,28 +757,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129000543</v>
+        <v>110044413</v>
       </c>
       <c r="B3" t="n">
-        <v>78801</v>
+        <v>93189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,38 +787,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>Rävabacken Utv, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>741337</v>
+        <v>741238</v>
       </c>
       <c r="R3" t="n">
-        <v>7294536</v>
+        <v>7294539</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -856,17 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,61 +861,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129000536</v>
+        <v>110044367</v>
       </c>
       <c r="B4" t="n">
-        <v>92835</v>
+        <v>93191</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>Rävabacken Utv, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>741464</v>
+        <v>741263</v>
       </c>
       <c r="R4" t="n">
-        <v>7294503</v>
+        <v>7294543</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,17 +938,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -987,22 +958,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129000537</v>
+        <v>110044387</v>
       </c>
       <c r="B5" t="n">
-        <v>92873</v>
+        <v>93191</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1010,38 +981,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>4362</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>Rävabacken Utv, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>741430</v>
+        <v>741505</v>
       </c>
       <c r="R5" t="n">
-        <v>7294484</v>
+        <v>7294450</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,17 +1035,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,22 +1055,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129000540</v>
+        <v>129000538</v>
       </c>
       <c r="B6" t="n">
-        <v>78802</v>
+        <v>93191</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1116,21 +1078,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>4362</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1144,10 +1106,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>741238</v>
+        <v>741402</v>
       </c>
       <c r="R6" t="n">
-        <v>7294334</v>
+        <v>7294418</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,10 +1173,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129000542</v>
+        <v>110044379</v>
       </c>
       <c r="B7" t="n">
-        <v>79663</v>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1222,38 +1184,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>Rävabacken Utv, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>741225</v>
+        <v>741287</v>
       </c>
       <c r="R7" t="n">
-        <v>7294470</v>
+        <v>7294517</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,17 +1238,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1305,44 +1258,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129000541</v>
+        <v>129000536</v>
       </c>
       <c r="B8" t="n">
-        <v>92847</v>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1356,10 +1309,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>741209</v>
+        <v>741464</v>
       </c>
       <c r="R8" t="n">
-        <v>7294469</v>
+        <v>7294503</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1423,10 +1376,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129000544</v>
+        <v>129000539</v>
       </c>
       <c r="B9" t="n">
-        <v>79663</v>
+        <v>93209</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1434,21 +1387,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>4366</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1462,10 +1415,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>741341</v>
+        <v>741260</v>
       </c>
       <c r="R9" t="n">
-        <v>7294535</v>
+        <v>7294367</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,14 +1482,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129000539</v>
+        <v>129000541</v>
       </c>
       <c r="B10" t="n">
-        <v>92847</v>
+        <v>93209</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1568,10 +1521,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>741260</v>
+        <v>741209</v>
       </c>
       <c r="R10" t="n">
-        <v>7294367</v>
+        <v>7294469</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1635,10 +1588,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129000538</v>
+        <v>129000537</v>
       </c>
       <c r="B11" t="n">
-        <v>92829</v>
+        <v>93235</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1646,21 +1599,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4362</v>
+        <v>5966</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1674,10 +1627,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>741402</v>
+        <v>741430</v>
       </c>
       <c r="R11" t="n">
-        <v>7294418</v>
+        <v>7294484</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1741,32 +1694,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131421828</v>
+        <v>131421831</v>
       </c>
       <c r="B12" t="n">
-        <v>79300</v>
+        <v>79373</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1776,10 +1729,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>741410</v>
+        <v>741264</v>
       </c>
       <c r="R12" t="n">
-        <v>7294501</v>
+        <v>7294336</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1838,32 +1791,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131421821</v>
+        <v>131421828</v>
       </c>
       <c r="B13" t="n">
-        <v>57914</v>
+        <v>79397</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1873,10 +1826,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>741194</v>
+        <v>741410</v>
       </c>
       <c r="R13" t="n">
-        <v>7294285</v>
+        <v>7294501</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1909,11 +1862,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack färska och gamla, tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1940,10 +1888,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131421825</v>
+        <v>129000543</v>
       </c>
       <c r="B14" t="n">
-        <v>57914</v>
+        <v>79084</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1951,37 +1899,41 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sarvasvägen, Nb</t>
+          <t>Grundsel, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>741401</v>
+        <v>741337</v>
       </c>
       <c r="R14" t="n">
-        <v>7294510</v>
+        <v>7294536</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2005,17 +1957,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Nya och gamla ringhack, rikligt, tall.</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2030,22 +1982,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131421830</v>
+        <v>129000542</v>
       </c>
       <c r="B15" t="n">
-        <v>91868</v>
+        <v>79946</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2053,33 +2005,41 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sarvasvägen, Nb</t>
+          <t>Grundsel, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>741165</v>
+        <v>741225</v>
       </c>
       <c r="R15" t="n">
-        <v>7294277</v>
+        <v>7294470</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2103,12 +2063,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2123,22 +2088,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131421824</v>
+        <v>129000544</v>
       </c>
       <c r="B16" t="n">
-        <v>57914</v>
+        <v>79946</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2146,37 +2111,41 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sarvasvägen, Nb</t>
+          <t>Grundsel, Nb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>741275</v>
+        <v>741341</v>
       </c>
       <c r="R16" t="n">
-        <v>7294333</v>
+        <v>7294535</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2200,17 +2169,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Gamla och nya ringhack, tallhed.</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2225,22 +2194,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131421831</v>
+        <v>131421821</v>
       </c>
       <c r="B17" t="n">
-        <v>79276</v>
+        <v>57975</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2248,21 +2217,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2272,10 +2241,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>741264</v>
+        <v>741194</v>
       </c>
       <c r="R17" t="n">
-        <v>7294336</v>
+        <v>7294285</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2308,6 +2277,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack färska och gamla, tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2334,48 +2308,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131421827</v>
+        <v>131421823</v>
       </c>
       <c r="B18" t="n">
-        <v>79345</v>
+        <v>57975</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>639</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grenlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Evernia mesomorpha</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sarvasvägen, Nb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>741351</v>
+        <v>741167</v>
       </c>
       <c r="R18" t="n">
-        <v>7294438</v>
+        <v>7294289</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2410,13 +2381,17 @@
           <t>2026-03-01</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Nya och gamla ringhack rikligt, tall</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2435,10 +2410,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131421823</v>
+        <v>131421824</v>
       </c>
       <c r="B19" t="n">
-        <v>57914</v>
+        <v>57975</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2470,10 +2445,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>741167</v>
+        <v>741275</v>
       </c>
       <c r="R19" t="n">
-        <v>7294289</v>
+        <v>7294333</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2510,7 +2485,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Nya och gamla ringhack rikligt, tall</t>
+          <t>Gamla och nya ringhack, tallhed.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2537,10 +2512,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132365428</v>
+        <v>131421825</v>
       </c>
       <c r="B20" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2566,27 +2541,19 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Väster om Sikträsket, Nb</t>
+          <t>Sarvasvägen, Nb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>741294</v>
+        <v>741401</v>
       </c>
       <c r="R20" t="n">
-        <v>7294330</v>
+        <v>7294510</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2620,7 +2587,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Flera ringhack på tall</t>
+          <t>Nya och gamla ringhack, rikligt, tall.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2635,12 +2602,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2650,7 +2617,7 @@
         <v>132365365</v>
       </c>
       <c r="B21" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2757,10 +2724,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132365494</v>
+        <v>132365428</v>
       </c>
       <c r="B22" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2790,20 +2757,20 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>SydVäst om Sikträsket, Nb</t>
+          <t>Väster om Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>741247</v>
+        <v>741294</v>
       </c>
       <c r="R22" t="n">
-        <v>7294318</v>
+        <v>7294330</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2840,14 +2807,14 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Flertalet ringhack på träd i direkt anslutning till bohålet</t>
+          <t>Flera ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="b">
         <v>0</v>
@@ -2864,6 +2831,539 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>132365494</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>SydVäst om Sikträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>741247</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7294318</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Flertalet ringhack på träd i direkt anslutning till bohålet</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>131421826</v>
+      </c>
+      <c r="B24" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Sarvasvägen, Nb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>741150</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7294265</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>132365028</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>SydVäst om Sikträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>741151</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7294262</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>110044410</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Rävabacken Utv, Nb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>741267</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7294536</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129000540</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Grundsel, Nb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>741238</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7294334</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51047-2025 artfynd.xlsx
+++ b/artfynd/A 51047-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131421827</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110044413</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110044367</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110044387</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1170,6 +1195,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000538</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1267,6 +1297,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110044379</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1373,6 +1408,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000536</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1479,6 +1519,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000539</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1585,6 +1630,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000541</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1691,6 +1741,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000537</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1788,6 +1843,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131421831</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1885,6 +1945,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131421828</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1991,6 +2056,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000543</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2097,6 +2167,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000542</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2203,6 +2278,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000544</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2305,6 +2385,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131421821</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2407,6 +2492,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131421823</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2509,6 +2599,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131421824</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2611,6 +2706,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131421825</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2721,6 +2821,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132365365</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2831,6 +2936,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132365428</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2941,6 +3051,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132365494</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3038,6 +3153,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131421826</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3161,6 +3281,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132365028</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3258,6 +3383,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110044410</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3364,8 +3494,41 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 51047-2025 artfynd.xlsx
+++ b/artfynd/A 51047-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ27"/>
+  <dimension ref="A1:AZ47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -786,48 +786,59 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110044413</v>
+        <v>135828232</v>
       </c>
       <c r="B3" t="n">
-        <v>93189</v>
+        <v>89327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>816</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Smultronkantarell</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Aphroditeola olida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Quél.) Redhead &amp; Manfr.Binder</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rävabacken Utv, Nb</t>
+          <t>SV Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>741238</v>
+        <v>741170</v>
       </c>
       <c r="R3" t="n">
-        <v>7294539</v>
+        <v>7294518</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -851,12 +862,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -865,33 +886,39 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110044413</t>
+          <t>https://artportalen.se/Sighting/135828232</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110044367</v>
+        <v>135828223</v>
       </c>
       <c r="B4" t="n">
-        <v>93191</v>
+        <v>87457</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,37 +926,48 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4362</v>
+        <v>3690</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Soop</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rävabacken Utv, Nb</t>
+          <t>SV Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>741263</v>
+        <v>741105</v>
       </c>
       <c r="R4" t="n">
-        <v>7294543</v>
+        <v>7294388</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -953,12 +991,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -967,33 +1015,39 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110044367</t>
+          <t>https://artportalen.se/Sighting/135828223</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110044387</v>
+        <v>110044413</v>
       </c>
       <c r="B5" t="n">
-        <v>93191</v>
+        <v>93189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,21 +1055,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1025,10 +1079,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>741505</v>
+        <v>741238</v>
       </c>
       <c r="R5" t="n">
-        <v>7294450</v>
+        <v>7294539</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,16 +1140,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110044387</t>
+          <t>https://artportalen.se/Sighting/110044413</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129000538</v>
+        <v>135825131</v>
       </c>
       <c r="B6" t="n">
-        <v>93191</v>
+        <v>93337</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1103,41 +1157,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>Sv Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>741402</v>
+        <v>741193</v>
       </c>
       <c r="R6" t="n">
-        <v>7294418</v>
+        <v>7294441</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1161,17 +1211,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1186,27 +1241,27 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000538</t>
+          <t>https://artportalen.se/Sighting/135825131</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>110044379</v>
+        <v>110044367</v>
       </c>
       <c r="B7" t="n">
-        <v>93197</v>
+        <v>93191</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1214,21 +1269,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1238,10 +1293,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>741287</v>
+        <v>741263</v>
       </c>
       <c r="R7" t="n">
-        <v>7294517</v>
+        <v>7294543</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1299,16 +1354,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110044379</t>
+          <t>https://artportalen.se/Sighting/110044367</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129000536</v>
+        <v>110044387</v>
       </c>
       <c r="B8" t="n">
-        <v>93197</v>
+        <v>93191</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1316,38 +1371,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>Rävabacken Utv, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>741464</v>
+        <v>741505</v>
       </c>
       <c r="R8" t="n">
-        <v>7294503</v>
+        <v>7294450</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1374,17 +1425,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1399,27 +1445,27 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000536</t>
+          <t>https://artportalen.se/Sighting/110044387</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129000539</v>
+        <v>129000538</v>
       </c>
       <c r="B9" t="n">
-        <v>93209</v>
+        <v>93191</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1427,21 +1473,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1455,10 +1501,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>741260</v>
+        <v>741402</v>
       </c>
       <c r="R9" t="n">
-        <v>7294367</v>
+        <v>7294418</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,16 +1567,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000539</t>
+          <t>https://artportalen.se/Sighting/129000538</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129000541</v>
+        <v>110044379</v>
       </c>
       <c r="B10" t="n">
-        <v>93209</v>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1538,38 +1584,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>Rävabacken Utv, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>741209</v>
+        <v>741287</v>
       </c>
       <c r="R10" t="n">
-        <v>7294469</v>
+        <v>7294517</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,17 +1638,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1621,27 +1658,27 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000541</t>
+          <t>https://artportalen.se/Sighting/110044379</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129000537</v>
+        <v>129000536</v>
       </c>
       <c r="B11" t="n">
-        <v>93235</v>
+        <v>93197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,21 +1686,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1677,10 +1714,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>741430</v>
+        <v>741464</v>
       </c>
       <c r="R11" t="n">
-        <v>7294484</v>
+        <v>7294503</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,54 +1780,54 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000537</t>
+          <t>https://artportalen.se/Sighting/129000536</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131421831</v>
+        <v>135825130</v>
       </c>
       <c r="B12" t="n">
-        <v>79373</v>
+        <v>93345</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sarvasvägen, Nb</t>
+          <t>Sv Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>741264</v>
+        <v>741149</v>
       </c>
       <c r="R12" t="n">
-        <v>7294336</v>
+        <v>7294363</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1814,12 +1851,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>20:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>20:05</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1845,54 +1892,54 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131421831</t>
+          <t>https://artportalen.se/Sighting/135825130</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131421828</v>
+        <v>135825132</v>
       </c>
       <c r="B13" t="n">
-        <v>79397</v>
+        <v>93345</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sarvasvägen, Nb</t>
+          <t>Sv Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>741410</v>
+        <v>741186</v>
       </c>
       <c r="R13" t="n">
-        <v>7294501</v>
+        <v>7294441</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1916,12 +1963,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1947,16 +2004,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131421828</t>
+          <t>https://artportalen.se/Sighting/135825132</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129000543</v>
+        <v>135828222</v>
       </c>
       <c r="B14" t="n">
-        <v>79084</v>
+        <v>93345</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1964,41 +2021,40 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>SV Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>741337</v>
+        <v>741097</v>
       </c>
       <c r="R14" t="n">
-        <v>7294536</v>
+        <v>7294374</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2022,17 +2078,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>19:37</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>19:37</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2041,33 +2102,39 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000543</t>
+          <t>https://artportalen.se/Sighting/135828222</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129000542</v>
+        <v>135828226</v>
       </c>
       <c r="B15" t="n">
-        <v>79946</v>
+        <v>93345</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2075,41 +2142,40 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>SV Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>741225</v>
+        <v>741113</v>
       </c>
       <c r="R15" t="n">
-        <v>7294470</v>
+        <v>7294382</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2133,17 +2199,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2152,33 +2223,39 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000542</t>
+          <t>https://artportalen.se/Sighting/135828226</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129000544</v>
+        <v>129000539</v>
       </c>
       <c r="B16" t="n">
-        <v>79946</v>
+        <v>93209</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2186,21 +2263,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>4366</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2214,10 +2291,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>741341</v>
+        <v>741260</v>
       </c>
       <c r="R16" t="n">
-        <v>7294535</v>
+        <v>7294367</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2280,16 +2357,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000544</t>
+          <t>https://artportalen.se/Sighting/129000539</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131421821</v>
+        <v>129000541</v>
       </c>
       <c r="B17" t="n">
-        <v>57975</v>
+        <v>93209</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2297,37 +2374,41 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>4366</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sarvasvägen, Nb</t>
+          <t>Grundsel, Nb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>741194</v>
+        <v>741209</v>
       </c>
       <c r="R17" t="n">
-        <v>7294285</v>
+        <v>7294469</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2351,17 +2432,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack färska och gamla, tall</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2376,27 +2457,27 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131421821</t>
+          <t>https://artportalen.se/Sighting/129000541</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131421823</v>
+        <v>129000537</v>
       </c>
       <c r="B18" t="n">
-        <v>57975</v>
+        <v>93235</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2404,37 +2485,41 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5966</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sarvasvägen, Nb</t>
+          <t>Grundsel, Nb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>741167</v>
+        <v>741430</v>
       </c>
       <c r="R18" t="n">
-        <v>7294289</v>
+        <v>7294484</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2458,17 +2543,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Nya och gamla ringhack rikligt, tall</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2483,49 +2568,49 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131421823</t>
+          <t>https://artportalen.se/Sighting/129000537</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131421824</v>
+        <v>131421831</v>
       </c>
       <c r="B19" t="n">
-        <v>57975</v>
+        <v>79373</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2535,10 +2620,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>741275</v>
+        <v>741264</v>
       </c>
       <c r="R19" t="n">
-        <v>7294333</v>
+        <v>7294336</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2573,11 +2658,6 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Gamla och nya ringhack, tallhed.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2601,38 +2681,38 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131421824</t>
+          <t>https://artportalen.se/Sighting/131421831</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131421825</v>
+        <v>131421828</v>
       </c>
       <c r="B20" t="n">
-        <v>57975</v>
+        <v>79397</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2642,10 +2722,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>741401</v>
+        <v>741410</v>
       </c>
       <c r="R20" t="n">
-        <v>7294510</v>
+        <v>7294501</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2680,11 +2760,6 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Nya och gamla ringhack, rikligt, tall.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2708,62 +2783,57 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131421825</t>
+          <t>https://artportalen.se/Sighting/131421828</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132365365</v>
+        <v>135828228</v>
       </c>
       <c r="B21" t="n">
-        <v>57975</v>
+        <v>79465</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Väster om Sikträsket, Nb</t>
+          <t>SV Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>741417</v>
+        <v>741122</v>
       </c>
       <c r="R21" t="n">
-        <v>7294498</v>
+        <v>7294378</v>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2787,17 +2857,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>19:58</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>19:58</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2806,8 +2881,29 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2817,22 +2913,22 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132365365</t>
+          <t>https://artportalen.se/Sighting/135828228</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132365428</v>
+        <v>135825128</v>
       </c>
       <c r="B22" t="n">
-        <v>57975</v>
+        <v>78844</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2840,45 +2936,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Väster om Sikträsket, Nb</t>
+          <t>Sv Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>741294</v>
+        <v>741118</v>
       </c>
       <c r="R22" t="n">
-        <v>7294330</v>
+        <v>7294382</v>
       </c>
       <c r="S22" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2902,17 +2990,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Flera ringhack på tall</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2927,27 +3020,27 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132365428</t>
+          <t>https://artportalen.se/Sighting/135825128</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132365494</v>
+        <v>129000543</v>
       </c>
       <c r="B23" t="n">
-        <v>57975</v>
+        <v>79084</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2955,45 +3048,41 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>SydVäst om Sikträsket, Nb</t>
+          <t>Grundsel, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>741247</v>
+        <v>741337</v>
       </c>
       <c r="R23" t="n">
-        <v>7294318</v>
+        <v>7294536</v>
       </c>
       <c r="S23" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3017,24 +3106,24 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Flertalet ringhack på träd i direkt anslutning till bohålet</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="b">
         <v>0</v>
@@ -3042,65 +3131,69 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132365494</t>
+          <t>https://artportalen.se/Sighting/129000543</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131421826</v>
+        <v>129000542</v>
       </c>
       <c r="B24" t="n">
-        <v>58131</v>
+        <v>79946</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103023</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sarvasvägen, Nb</t>
+          <t>Grundsel, Nb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>741150</v>
+        <v>741225</v>
       </c>
       <c r="R24" t="n">
-        <v>7294265</v>
+        <v>7294470</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3124,12 +3217,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3144,78 +3242,66 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131421826</t>
+          <t>https://artportalen.se/Sighting/129000542</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132365028</v>
+        <v>129000544</v>
       </c>
       <c r="B25" t="n">
-        <v>58131</v>
+        <v>79946</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103023</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>SydVäst om Sikträsket, Nb</t>
+          <t>Grundsel, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>741151</v>
+        <v>741341</v>
       </c>
       <c r="R25" t="n">
-        <v>7294262</v>
+        <v>7294535</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3242,22 +3328,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>13:02</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>13:02</t>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3272,27 +3353,27 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132365028</t>
+          <t>https://artportalen.se/Sighting/129000544</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>110044410</v>
+        <v>135825127</v>
       </c>
       <c r="B26" t="n">
-        <v>58057</v>
+        <v>78445</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3300,37 +3381,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103031</v>
+        <v>6487</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Rävabacken Utv, Nb</t>
+          <t>Sv Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>741267</v>
+        <v>741118</v>
       </c>
       <c r="R26" t="n">
-        <v>7294536</v>
+        <v>7294382</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3354,12 +3435,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3374,27 +3465,27 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110044410</t>
+          <t>https://artportalen.se/Sighting/135825127</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129000540</v>
+        <v>131421821</v>
       </c>
       <c r="B27" t="n">
-        <v>79085</v>
+        <v>57975</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3402,41 +3493,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>Sarvasvägen, Nb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>741238</v>
+        <v>741194</v>
       </c>
       <c r="R27" t="n">
-        <v>7294334</v>
+        <v>7294285</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3460,17 +3547,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Ringhack färska och gamla, tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3485,18 +3572,2387 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/131421821</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>131421823</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Sarvasvägen, Nb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>741167</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7294289</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Nya och gamla ringhack rikligt, tall</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131421823</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>131421824</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Sarvasvägen, Nb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>741275</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7294333</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Gamla och nya ringhack, tallhed.</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131421824</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>131421825</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Sarvasvägen, Nb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>741401</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7294510</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Nya och gamla ringhack, rikligt, tall.</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131421825</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>132365365</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Väster om Sikträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>741417</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7294498</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132365365</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>132365428</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Väster om Sikträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>741294</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7294330</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Flera ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132365428</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>132365494</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>SydVäst om Sikträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>741247</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7294318</v>
+      </c>
+      <c r="S33" t="n">
+        <v>1</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Flertalet ringhack på träd i direkt anslutning till bohålet</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132365494</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>135825133</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Sv Sikträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>741176</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7294442</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>20:17</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>20:17</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Färska och gamla ringhack</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135825133</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135828227</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>SV Sikträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>741122</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7294378</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135828227</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135828230</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>SV Sikträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>741155</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7294379</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>20:06</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>20:06</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135828230</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>135828231</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>SV Sikträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>741186</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7294423</v>
+      </c>
+      <c r="S37" t="n">
+        <v>6</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>20:11</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>20:11</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135828231</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>135825126</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Sv Sikträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>741114</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7294391</v>
+      </c>
+      <c r="S38" t="n">
+        <v>6</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>19:48</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>19:48</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135825126</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>135857317</v>
+      </c>
+      <c r="B39" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>SV Sikträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>741177</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7294392</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>20:09</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>20:09</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Lockläten</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135857317</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>131421826</v>
+      </c>
+      <c r="B40" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Sarvasvägen, Nb</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>741150</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7294265</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131421826</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>132365028</v>
+      </c>
+      <c r="B41" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>SydVäst om Sikträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>741151</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7294262</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132365028</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>110044410</v>
+      </c>
+      <c r="B42" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Rävabacken Utv, Nb</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>741267</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7294536</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110044410</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135828221</v>
+      </c>
+      <c r="B43" t="n">
+        <v>98136</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>SV Sikträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>741098</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7294366</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135828221</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>129000540</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Grundsel, Nb</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>741238</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7294334</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/129000540</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>135828224</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>SV Sikträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>741114</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7294379</v>
+      </c>
+      <c r="S45" t="n">
+        <v>6</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135828224</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>135828225</v>
+      </c>
+      <c r="B46" t="n">
+        <v>80031</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>SV Sikträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>741106</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7294382</v>
+      </c>
+      <c r="S46" t="n">
+        <v>7</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>19:54</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>19:54</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135828225</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>135825134</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79464</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Sv Sikträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>741168</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7294460</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135825134</t>
         </is>
       </c>
     </row>
@@ -3528,6 +5984,26 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51047-2025 artfynd.xlsx
+++ b/artfynd/A 51047-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>135828232</v>
       </c>
       <c r="B3" t="n">
-        <v>89327</v>
+        <v>89329</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>135828223</v>
       </c>
       <c r="B4" t="n">
-        <v>87457</v>
+        <v>87458</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>135825131</v>
       </c>
       <c r="B6" t="n">
-        <v>93337</v>
+        <v>93339</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>135825130</v>
       </c>
       <c r="B12" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>135825132</v>
       </c>
       <c r="B13" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         <v>135828222</v>
       </c>
       <c r="B14" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>135828226</v>
       </c>
       <c r="B15" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         <v>135828221</v>
       </c>
       <c r="B43" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 51047-2025 artfynd.xlsx
+++ b/artfynd/A 51047-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ47"/>
+  <dimension ref="A1:AZ53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,51 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131421827</v>
+        <v>135825129</v>
       </c>
       <c r="B2" t="n">
-        <v>79442</v>
+        <v>83420</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>639</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grenlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Evernia mesomorpha</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Nyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sarvasvägen, Nb</t>
+          <t>Sv Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>741351</v>
+        <v>741142</v>
       </c>
       <c r="R2" t="n">
-        <v>7294438</v>
+        <v>7294368</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,12 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,65 +787,54 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131421827</t>
+          <t>https://artportalen.se/Sighting/135825129</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135828232</v>
+        <v>135825124</v>
       </c>
       <c r="B3" t="n">
-        <v>89329</v>
+        <v>79107</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>816</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Smultronkantarell</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Aphroditeola olida</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Quél.) Redhead &amp; Manfr.Binder</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>SV Sikträsket, Nb</t>
+          <t>Sv Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>741170</v>
+        <v>741095</v>
       </c>
       <c r="R3" t="n">
-        <v>7294518</v>
+        <v>7294406</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +863,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +873,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,85 +882,71 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135828232</t>
+          <t>https://artportalen.se/Sighting/135825124</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135828223</v>
+        <v>131421827</v>
       </c>
       <c r="B4" t="n">
-        <v>87458</v>
+        <v>79442</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3690</v>
+        <v>639</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Grenlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Evernia mesomorpha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Soop</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Nyl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>SV Sikträsket, Nb</t>
+          <t>Sarvasvägen, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>741105</v>
+        <v>741351</v>
       </c>
       <c r="R4" t="n">
-        <v>7294388</v>
+        <v>7294438</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -991,22 +973,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>19:39</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>19:39</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,73 +991,79 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
-      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135828223</t>
+          <t>https://artportalen.se/Sighting/131421827</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110044413</v>
+        <v>135828232</v>
       </c>
       <c r="B5" t="n">
-        <v>93189</v>
+        <v>89329</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4361</v>
+        <v>816</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Smultronkantarell</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Aphroditeola olida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Quél.) Redhead &amp; Manfr.Binder</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rävabacken Utv, Nb</t>
+          <t>SV Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>741238</v>
+        <v>741170</v>
       </c>
       <c r="R5" t="n">
-        <v>7294539</v>
+        <v>7294518</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1109,12 +1087,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,33 +1111,39 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110044413</t>
+          <t>https://artportalen.se/Sighting/135828232</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135825131</v>
+        <v>135825122</v>
       </c>
       <c r="B6" t="n">
-        <v>93339</v>
+        <v>91972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1157,21 +1151,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4361</v>
+        <v>3242</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1181,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>741193</v>
+        <v>741077</v>
       </c>
       <c r="R6" t="n">
-        <v>7294441</v>
+        <v>7294449</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1216,7 +1210,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1226,7 +1220,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1252,16 +1246,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825131</t>
+          <t>https://artportalen.se/Sighting/135825122</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>110044367</v>
+        <v>135828223</v>
       </c>
       <c r="B7" t="n">
-        <v>93191</v>
+        <v>87458</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,37 +1263,48 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4362</v>
+        <v>3690</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Soop</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rävabacken Utv, Nb</t>
+          <t>SV Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>741263</v>
+        <v>741105</v>
       </c>
       <c r="R7" t="n">
-        <v>7294543</v>
+        <v>7294388</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1323,12 +1328,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,33 +1352,39 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110044367</t>
+          <t>https://artportalen.se/Sighting/135828223</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>110044387</v>
+        <v>110044413</v>
       </c>
       <c r="B8" t="n">
-        <v>93191</v>
+        <v>93189</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1371,21 +1392,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1395,10 +1416,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>741505</v>
+        <v>741238</v>
       </c>
       <c r="R8" t="n">
-        <v>7294450</v>
+        <v>7294539</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1456,16 +1477,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110044387</t>
+          <t>https://artportalen.se/Sighting/110044413</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129000538</v>
+        <v>135825131</v>
       </c>
       <c r="B9" t="n">
-        <v>93191</v>
+        <v>93339</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1473,41 +1494,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>Sv Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>741402</v>
+        <v>741193</v>
       </c>
       <c r="R9" t="n">
-        <v>7294418</v>
+        <v>7294441</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1531,17 +1548,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1556,27 +1578,27 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000538</t>
+          <t>https://artportalen.se/Sighting/135825131</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>110044379</v>
+        <v>110044367</v>
       </c>
       <c r="B10" t="n">
-        <v>93197</v>
+        <v>93191</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1584,21 +1606,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1608,10 +1630,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>741287</v>
+        <v>741263</v>
       </c>
       <c r="R10" t="n">
-        <v>7294517</v>
+        <v>7294543</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,16 +1691,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110044379</t>
+          <t>https://artportalen.se/Sighting/110044367</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129000536</v>
+        <v>110044387</v>
       </c>
       <c r="B11" t="n">
-        <v>93197</v>
+        <v>93191</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1686,38 +1708,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>Rävabacken Utv, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>741464</v>
+        <v>741505</v>
       </c>
       <c r="R11" t="n">
-        <v>7294503</v>
+        <v>7294450</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1744,17 +1762,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1769,27 +1782,27 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000536</t>
+          <t>https://artportalen.se/Sighting/110044387</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135825130</v>
+        <v>129000538</v>
       </c>
       <c r="B12" t="n">
-        <v>93347</v>
+        <v>93191</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1797,37 +1810,41 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sv Sikträskberget, Nb</t>
+          <t>Grundsel, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>741149</v>
+        <v>741402</v>
       </c>
       <c r="R12" t="n">
-        <v>7294363</v>
+        <v>7294418</v>
       </c>
       <c r="S12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1851,22 +1868,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>20:05</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>20:05</t>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1881,27 +1893,27 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825130</t>
+          <t>https://artportalen.se/Sighting/129000538</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135825132</v>
+        <v>110044379</v>
       </c>
       <c r="B13" t="n">
-        <v>93347</v>
+        <v>93197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1929,17 +1941,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sv Sikträskberget, Nb</t>
+          <t>Rävabacken Utv, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>741186</v>
+        <v>741287</v>
       </c>
       <c r="R13" t="n">
-        <v>7294441</v>
+        <v>7294517</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1963,22 +1975,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>20:14</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>20:14</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1993,27 +1995,27 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825132</t>
+          <t>https://artportalen.se/Sighting/110044379</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135828222</v>
+        <v>129000536</v>
       </c>
       <c r="B14" t="n">
-        <v>93347</v>
+        <v>93197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2038,23 +2040,24 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>SV Sikträsket, Nb</t>
+          <t>Grundsel, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>741097</v>
+        <v>741464</v>
       </c>
       <c r="R14" t="n">
-        <v>7294374</v>
+        <v>7294503</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2078,22 +2081,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>19:37</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>19:37</t>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2102,36 +2100,30 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135828222</t>
+          <t>https://artportalen.se/Sighting/129000536</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135828226</v>
+        <v>135825120</v>
       </c>
       <c r="B15" t="n">
         <v>93347</v>
@@ -2160,22 +2152,19 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>SV Sikträsket, Nb</t>
+          <t>Sv Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>741113</v>
+        <v>741122</v>
       </c>
       <c r="R15" t="n">
-        <v>7294382</v>
+        <v>7294512</v>
       </c>
       <c r="S15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2204,7 +2193,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2214,7 +2203,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2223,39 +2212,33 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135828226</t>
+          <t>https://artportalen.se/Sighting/135825120</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129000539</v>
+        <v>135825130</v>
       </c>
       <c r="B16" t="n">
-        <v>93209</v>
+        <v>93347</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2263,41 +2246,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>Sv Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>741260</v>
+        <v>741149</v>
       </c>
       <c r="R16" t="n">
-        <v>7294367</v>
+        <v>7294363</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2321,17 +2300,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>20:05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>20:05</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2346,27 +2330,27 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000539</t>
+          <t>https://artportalen.se/Sighting/135825130</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129000541</v>
+        <v>135825132</v>
       </c>
       <c r="B17" t="n">
-        <v>93209</v>
+        <v>93347</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2374,41 +2358,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>Sv Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>741209</v>
+        <v>741186</v>
       </c>
       <c r="R17" t="n">
-        <v>7294469</v>
+        <v>7294441</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2432,17 +2412,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2457,27 +2442,27 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000541</t>
+          <t>https://artportalen.se/Sighting/135825132</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129000537</v>
+        <v>135828222</v>
       </c>
       <c r="B18" t="n">
-        <v>93235</v>
+        <v>93347</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2485,41 +2470,40 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>SV Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>741430</v>
+        <v>741097</v>
       </c>
       <c r="R18" t="n">
-        <v>7294484</v>
+        <v>7294374</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2543,17 +2527,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>19:37</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>19:37</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2562,71 +2551,80 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000537</t>
+          <t>https://artportalen.se/Sighting/135828222</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131421831</v>
+        <v>135828226</v>
       </c>
       <c r="B19" t="n">
-        <v>79373</v>
+        <v>93347</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sarvasvägen, Nb</t>
+          <t>SV Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>741264</v>
+        <v>741113</v>
       </c>
       <c r="R19" t="n">
-        <v>7294336</v>
+        <v>7294382</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2650,12 +2648,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2664,71 +2672,81 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131421831</t>
+          <t>https://artportalen.se/Sighting/135828226</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131421828</v>
+        <v>129000539</v>
       </c>
       <c r="B20" t="n">
-        <v>79397</v>
+        <v>93209</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6434</v>
+        <v>4366</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sarvasvägen, Nb</t>
+          <t>Grundsel, Nb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>741410</v>
+        <v>741260</v>
       </c>
       <c r="R20" t="n">
-        <v>7294501</v>
+        <v>7294367</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2752,12 +2770,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2772,68 +2795,69 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131421828</t>
+          <t>https://artportalen.se/Sighting/129000539</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135828228</v>
+        <v>129000541</v>
       </c>
       <c r="B21" t="n">
-        <v>79465</v>
+        <v>93209</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6434</v>
+        <v>4366</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>SV Sikträsket, Nb</t>
+          <t>Grundsel, Nb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>741122</v>
+        <v>741209</v>
       </c>
       <c r="R21" t="n">
-        <v>7294378</v>
+        <v>7294469</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2857,22 +2881,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>19:58</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>19:58</t>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2881,78 +2900,53 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135828228</t>
+          <t>https://artportalen.se/Sighting/129000541</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135825128</v>
+        <v>135825125</v>
       </c>
       <c r="B22" t="n">
-        <v>78844</v>
+        <v>93376</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6437</v>
+        <v>5449</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2960,10 +2954,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>741118</v>
+        <v>741107</v>
       </c>
       <c r="R22" t="n">
-        <v>7294382</v>
+        <v>7294391</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2995,7 +2989,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3005,7 +2999,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>19:44</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>och äldre fruktkropp</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3031,58 +3030,54 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825128</t>
+          <t>https://artportalen.se/Sighting/135825125</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129000543</v>
+        <v>135825123</v>
       </c>
       <c r="B23" t="n">
-        <v>79084</v>
+        <v>91421</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>5685</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>Sv Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>741337</v>
+        <v>741088</v>
       </c>
       <c r="R23" t="n">
-        <v>7294536</v>
+        <v>7294391</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3106,17 +3101,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3131,27 +3131,27 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000543</t>
+          <t>https://artportalen.se/Sighting/135825123</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129000542</v>
+        <v>129000537</v>
       </c>
       <c r="B24" t="n">
-        <v>79946</v>
+        <v>93235</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3159,21 +3159,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>741225</v>
+        <v>741430</v>
       </c>
       <c r="R24" t="n">
-        <v>7294470</v>
+        <v>7294484</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3253,58 +3253,54 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000542</t>
+          <t>https://artportalen.se/Sighting/129000537</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129000544</v>
+        <v>131421831</v>
       </c>
       <c r="B25" t="n">
-        <v>79946</v>
+        <v>79373</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>Sarvasvägen, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>741341</v>
+        <v>741264</v>
       </c>
       <c r="R25" t="n">
-        <v>7294535</v>
+        <v>7294336</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3328,17 +3324,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3353,65 +3344,65 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000544</t>
+          <t>https://artportalen.se/Sighting/131421831</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135825127</v>
+        <v>131421828</v>
       </c>
       <c r="B26" t="n">
-        <v>78445</v>
+        <v>79397</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6487</v>
+        <v>6434</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sv Sikträskberget, Nb</t>
+          <t>Sarvasvägen, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>741118</v>
+        <v>741410</v>
       </c>
       <c r="R26" t="n">
-        <v>7294382</v>
+        <v>7294501</v>
       </c>
       <c r="S26" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3435,22 +3426,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>19:55</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>19:55</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3476,51 +3457,54 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825127</t>
+          <t>https://artportalen.se/Sighting/131421828</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131421821</v>
+        <v>135828228</v>
       </c>
       <c r="B27" t="n">
-        <v>57975</v>
+        <v>79465</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sarvasvägen, Nb</t>
+          <t>SV Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>741194</v>
+        <v>741122</v>
       </c>
       <c r="R27" t="n">
-        <v>7294285</v>
+        <v>7294378</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3547,17 +3531,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>19:58</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack färska och gamla, tall</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>19:58</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3566,33 +3555,54 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131421821</t>
+          <t>https://artportalen.se/Sighting/135828228</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131421823</v>
+        <v>135825128</v>
       </c>
       <c r="B28" t="n">
-        <v>57975</v>
+        <v>78844</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3600,34 +3610,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Sarvasvägen, Nb</t>
+          <t>Sv Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>741167</v>
+        <v>741118</v>
       </c>
       <c r="R28" t="n">
-        <v>7294289</v>
+        <v>7294382</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3654,17 +3664,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Nya och gamla ringhack rikligt, tall</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3690,16 +3705,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131421823</t>
+          <t>https://artportalen.se/Sighting/135825128</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131421824</v>
+        <v>129000543</v>
       </c>
       <c r="B29" t="n">
-        <v>57975</v>
+        <v>79084</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3707,37 +3722,41 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sarvasvägen, Nb</t>
+          <t>Grundsel, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>741275</v>
+        <v>741337</v>
       </c>
       <c r="R29" t="n">
-        <v>7294333</v>
+        <v>7294536</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3761,17 +3780,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Gamla och nya ringhack, tallhed.</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3786,27 +3805,27 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131421824</t>
+          <t>https://artportalen.se/Sighting/129000543</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131421825</v>
+        <v>129000542</v>
       </c>
       <c r="B30" t="n">
-        <v>57975</v>
+        <v>79946</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3814,37 +3833,41 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Sarvasvägen, Nb</t>
+          <t>Grundsel, Nb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>741401</v>
+        <v>741225</v>
       </c>
       <c r="R30" t="n">
-        <v>7294510</v>
+        <v>7294470</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3868,17 +3891,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Nya och gamla ringhack, rikligt, tall.</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3893,27 +3916,27 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131421825</t>
+          <t>https://artportalen.se/Sighting/129000542</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132365365</v>
+        <v>129000544</v>
       </c>
       <c r="B31" t="n">
-        <v>57975</v>
+        <v>79946</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3921,45 +3944,41 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Väster om Sikträsket, Nb</t>
+          <t>Grundsel, Nb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>741417</v>
+        <v>741341</v>
       </c>
       <c r="R31" t="n">
-        <v>7294498</v>
+        <v>7294535</v>
       </c>
       <c r="S31" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3983,17 +4002,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4008,27 +4027,27 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132365365</t>
+          <t>https://artportalen.se/Sighting/129000544</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132365428</v>
+        <v>135825121</v>
       </c>
       <c r="B32" t="n">
-        <v>57975</v>
+        <v>80060</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4036,45 +4055,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Väster om Sikträsket, Nb</t>
+          <t>Sv Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>741294</v>
+        <v>741110</v>
       </c>
       <c r="R32" t="n">
-        <v>7294330</v>
+        <v>7294497</v>
       </c>
       <c r="S32" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4098,17 +4109,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Flera ringhack på tall</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4123,27 +4139,27 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132365428</t>
+          <t>https://artportalen.se/Sighting/135825121</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132365494</v>
+        <v>135825127</v>
       </c>
       <c r="B33" t="n">
-        <v>57975</v>
+        <v>78445</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4151,45 +4167,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>SydVäst om Sikträsket, Nb</t>
+          <t>Sv Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>741247</v>
+        <v>741118</v>
       </c>
       <c r="R33" t="n">
-        <v>7294318</v>
+        <v>7294382</v>
       </c>
       <c r="S33" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4213,24 +4221,29 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Flertalet ringhack på träd i direkt anslutning till bohålet</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="b">
         <v>0</v>
@@ -4238,27 +4251,27 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132365494</t>
+          <t>https://artportalen.se/Sighting/135825127</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135825133</v>
+        <v>131421821</v>
       </c>
       <c r="B34" t="n">
-        <v>57980</v>
+        <v>57975</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4286,14 +4299,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sv Sikträskberget, Nb</t>
+          <t>Sarvasvägen, Nb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>741176</v>
+        <v>741194</v>
       </c>
       <c r="R34" t="n">
-        <v>7294442</v>
+        <v>7294285</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4320,27 +4333,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>20:17</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>20:17</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Färska och gamla ringhack</t>
+          <t>Ringhack färska och gamla, tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4366,16 +4369,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825133</t>
+          <t>https://artportalen.se/Sighting/131421821</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135828227</v>
+        <v>131421823</v>
       </c>
       <c r="B35" t="n">
-        <v>57980</v>
+        <v>57975</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4401,24 +4404,16 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>SV Sikträsket, Nb</t>
+          <t>Sarvasvägen, Nb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>741122</v>
+        <v>741167</v>
       </c>
       <c r="R35" t="n">
-        <v>7294378</v>
+        <v>7294289</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4445,27 +4440,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>19:58</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>19:58</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Nya och gamla ringhack rikligt, tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4476,51 +4461,31 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135828227</t>
+          <t>https://artportalen.se/Sighting/131421823</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135828230</v>
+        <v>131421824</v>
       </c>
       <c r="B36" t="n">
-        <v>57980</v>
+        <v>57975</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4546,24 +4511,16 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>SV Sikträsket, Nb</t>
+          <t>Sarvasvägen, Nb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>741155</v>
+        <v>741275</v>
       </c>
       <c r="R36" t="n">
-        <v>7294379</v>
+        <v>7294333</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4590,27 +4547,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>20:06</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>20:06</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>Gamla och nya ringhack, tallhed.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4621,51 +4568,31 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135828230</t>
+          <t>https://artportalen.se/Sighting/131421824</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135828231</v>
+        <v>131421825</v>
       </c>
       <c r="B37" t="n">
-        <v>57980</v>
+        <v>57975</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4691,27 +4618,19 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>SV Sikträsket, Nb</t>
+          <t>Sarvasvägen, Nb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>741186</v>
+        <v>741401</v>
       </c>
       <c r="R37" t="n">
-        <v>7294423</v>
+        <v>7294510</v>
       </c>
       <c r="S37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4735,27 +4654,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>20:11</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>20:11</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Nya och gamla ringhack, rikligt, tall.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4766,79 +4675,77 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135828231</t>
+          <t>https://artportalen.se/Sighting/131421825</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135825126</v>
+        <v>132365365</v>
       </c>
       <c r="B38" t="n">
-        <v>57167</v>
+        <v>57975</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sv Sikträskberget, Nb</t>
+          <t>Väster om Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>741114</v>
+        <v>741417</v>
       </c>
       <c r="R38" t="n">
-        <v>7294391</v>
+        <v>7294498</v>
       </c>
       <c r="S38" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4862,22 +4769,17 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>19:48</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>19:48</t>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4892,27 +4794,27 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825126</t>
+          <t>https://artportalen.se/Sighting/132365365</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135857317</v>
+        <v>132365428</v>
       </c>
       <c r="B39" t="n">
-        <v>58141</v>
+        <v>57975</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4920,21 +4822,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4942,23 +4844,23 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>SV Sikträsket, Nb</t>
+          <t>Väster om Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>741177</v>
+        <v>741294</v>
       </c>
       <c r="R39" t="n">
-        <v>7294392</v>
+        <v>7294330</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4982,27 +4884,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>20:09</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>20:09</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Lockläten</t>
+          <t>Flera ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5013,11 +4905,6 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5027,39 +4914,39 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135857317</t>
+          <t>https://artportalen.se/Sighting/132365428</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131421826</v>
+        <v>132365494</v>
       </c>
       <c r="B40" t="n">
-        <v>58131</v>
+        <v>57975</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103023</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5068,19 +4955,27 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Sarvasvägen, Nb</t>
+          <t>SydVäst om Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>741150</v>
+        <v>741247</v>
       </c>
       <c r="R40" t="n">
-        <v>7294265</v>
+        <v>7294318</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5112,11 +5007,16 @@
           <t>2026-03-01</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Flertalet ringhack på träd i direkt anslutning till bohålet</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG40" t="b">
         <v>0</v>
@@ -5124,44 +5024,44 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131421826</t>
+          <t>https://artportalen.se/Sighting/132365494</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132365028</v>
+        <v>135825133</v>
       </c>
       <c r="B41" t="n">
-        <v>58131</v>
+        <v>57980</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103023</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5169,36 +5069,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>SydVäst om Sikträsket, Nb</t>
+          <t>Sv Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>741151</v>
+        <v>741176</v>
       </c>
       <c r="R41" t="n">
-        <v>7294262</v>
+        <v>7294442</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5222,22 +5106,27 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>20:17</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>20:17</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Färska och gamla ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5252,27 +5141,27 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132365028</t>
+          <t>https://artportalen.se/Sighting/135825133</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>110044410</v>
+        <v>135828227</v>
       </c>
       <c r="B42" t="n">
-        <v>58057</v>
+        <v>57980</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5280,16 +5169,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5298,19 +5187,27 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Rävabacken Utv, Nb</t>
+          <t>SV Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>741267</v>
+        <v>741122</v>
       </c>
       <c r="R42" t="n">
-        <v>7294536</v>
+        <v>7294378</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5334,12 +5231,27 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>19:58</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5350,59 +5262,83 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110044410</t>
+          <t>https://artportalen.se/Sighting/135828227</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135828221</v>
+        <v>135828230</v>
       </c>
       <c r="B43" t="n">
-        <v>98138</v>
+        <v>57980</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5410,10 +5346,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>741098</v>
+        <v>741155</v>
       </c>
       <c r="R43" t="n">
-        <v>7294366</v>
+        <v>7294379</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5445,7 +5381,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5455,7 +5391,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>20:06</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5464,13 +5405,27 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
           <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5487,16 +5442,16 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135828221</t>
+          <t>https://artportalen.se/Sighting/135828230</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129000540</v>
+        <v>135828231</v>
       </c>
       <c r="B44" t="n">
-        <v>79085</v>
+        <v>57980</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5504,41 +5459,45 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>SV Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>741238</v>
+        <v>741186</v>
       </c>
       <c r="R44" t="n">
-        <v>7294334</v>
+        <v>7294423</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5562,17 +5521,27 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5583,69 +5552,76 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000540</t>
+          <t>https://artportalen.se/Sighting/135828231</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135828224</v>
+        <v>135825126</v>
       </c>
       <c r="B45" t="n">
-        <v>79199</v>
+        <v>57167</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>SV Sikträsket, Nb</t>
+          <t>Sv Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q45" t="n">
         <v>741114</v>
       </c>
       <c r="R45" t="n">
-        <v>7294379</v>
+        <v>7294391</v>
       </c>
       <c r="S45" t="n">
         <v>6</v>
@@ -5677,7 +5653,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5687,7 +5663,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5696,39 +5672,33 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135828224</t>
+          <t>https://artportalen.se/Sighting/135825126</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135828225</v>
+        <v>135857317</v>
       </c>
       <c r="B46" t="n">
-        <v>80031</v>
+        <v>58141</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5736,26 +5706,31 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>229821</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5763,13 +5738,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>741106</v>
+        <v>741177</v>
       </c>
       <c r="R46" t="n">
-        <v>7294382</v>
+        <v>7294392</v>
       </c>
       <c r="S46" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5798,7 +5773,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>19:54</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5808,7 +5783,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>19:54</t>
+          <t>20:09</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Lockläten</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5817,7 +5797,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5840,51 +5819,51 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135828225</t>
+          <t>https://artportalen.se/Sighting/135857317</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135825134</v>
+        <v>131421826</v>
       </c>
       <c r="B47" t="n">
-        <v>79464</v>
+        <v>58131</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>260591</v>
+        <v>103023</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sv Sikträskberget, Nb</t>
+          <t>Sarvasvägen, Nb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>741168</v>
+        <v>741150</v>
       </c>
       <c r="R47" t="n">
-        <v>7294460</v>
+        <v>7294265</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5911,22 +5890,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>20:20</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>20:20</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5951,6 +5920,702 @@
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131421826</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>132365028</v>
+      </c>
+      <c r="B48" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>SydVäst om Sikträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>741151</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7294262</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132365028</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>110044410</v>
+      </c>
+      <c r="B49" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Rävabacken Utv, Nb</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>741267</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7294536</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110044410</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>135828221</v>
+      </c>
+      <c r="B50" t="n">
+        <v>98138</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>SV Sikträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>741098</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7294366</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135828221</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>129000540</v>
+      </c>
+      <c r="B51" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Grundsel, Nb</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>741238</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7294334</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000540</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>135828224</v>
+      </c>
+      <c r="B52" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>SV Sikträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>741114</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7294379</v>
+      </c>
+      <c r="S52" t="n">
+        <v>6</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135828224</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>135825134</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79464</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Sv Sikträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>741168</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7294460</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135825134</t>
         </is>
@@ -6004,6 +6669,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51047-2025 artfynd.xlsx
+++ b/artfynd/A 51047-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ53"/>
+  <dimension ref="A1:AZ52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1140,10 +1140,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135825122</v>
+        <v>135828223</v>
       </c>
       <c r="B6" t="n">
-        <v>91972</v>
+        <v>87458</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1151,34 +1151,45 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3242</v>
+        <v>3690</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Soop</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sv Sikträskberget, Nb</t>
+          <t>SV Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>741077</v>
+        <v>741105</v>
       </c>
       <c r="R6" t="n">
-        <v>7294449</v>
+        <v>7294388</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1210,7 +1221,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1220,7 +1231,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,33 +1240,39 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825122</t>
+          <t>https://artportalen.se/Sighting/135828223</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135828223</v>
+        <v>110044413</v>
       </c>
       <c r="B7" t="n">
-        <v>87458</v>
+        <v>93189</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1263,48 +1280,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3690</v>
+        <v>4361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Soop</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>SV Sikträsket, Nb</t>
+          <t>Rävabacken Utv, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>741105</v>
+        <v>741238</v>
       </c>
       <c r="R7" t="n">
-        <v>7294388</v>
+        <v>7294539</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1328,22 +1334,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>19:39</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>19:39</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,39 +1348,33 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135828223</t>
+          <t>https://artportalen.se/Sighting/110044413</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>110044413</v>
+        <v>135825131</v>
       </c>
       <c r="B8" t="n">
-        <v>93189</v>
+        <v>93339</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,17 +1402,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rävabacken Utv, Nb</t>
+          <t>Sv Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>741238</v>
+        <v>741193</v>
       </c>
       <c r="R8" t="n">
-        <v>7294539</v>
+        <v>7294441</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1446,12 +1436,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,27 +1466,27 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110044413</t>
+          <t>https://artportalen.se/Sighting/135825131</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135825131</v>
+        <v>110044367</v>
       </c>
       <c r="B9" t="n">
-        <v>93339</v>
+        <v>93191</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,37 +1494,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sv Sikträskberget, Nb</t>
+          <t>Rävabacken Utv, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>741193</v>
+        <v>741263</v>
       </c>
       <c r="R9" t="n">
-        <v>7294441</v>
+        <v>7294543</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1548,22 +1548,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>20:12</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>20:12</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1578,24 +1568,24 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825131</t>
+          <t>https://artportalen.se/Sighting/110044367</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>110044367</v>
+        <v>110044387</v>
       </c>
       <c r="B10" t="n">
         <v>93191</v>
@@ -1630,10 +1620,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>741263</v>
+        <v>741505</v>
       </c>
       <c r="R10" t="n">
-        <v>7294543</v>
+        <v>7294450</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1691,13 +1681,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110044367</t>
+          <t>https://artportalen.se/Sighting/110044387</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>110044387</v>
+        <v>129000538</v>
       </c>
       <c r="B11" t="n">
         <v>93191</v>
@@ -1725,17 +1715,21 @@
           <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rävabacken Utv, Nb</t>
+          <t>Grundsel, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>741505</v>
+        <v>741402</v>
       </c>
       <c r="R11" t="n">
-        <v>7294450</v>
+        <v>7294418</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1762,12 +1756,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1782,27 +1781,27 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110044387</t>
+          <t>https://artportalen.se/Sighting/129000538</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129000538</v>
+        <v>110044379</v>
       </c>
       <c r="B12" t="n">
-        <v>93191</v>
+        <v>93197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1810,38 +1809,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>Rävabacken Utv, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>741402</v>
+        <v>741287</v>
       </c>
       <c r="R12" t="n">
-        <v>7294418</v>
+        <v>7294517</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1868,17 +1863,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1893,24 +1883,24 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000538</t>
+          <t>https://artportalen.se/Sighting/110044379</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>110044379</v>
+        <v>129000536</v>
       </c>
       <c r="B13" t="n">
         <v>93197</v>
@@ -1938,17 +1928,21 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Rävabacken Utv, Nb</t>
+          <t>Grundsel, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>741287</v>
+        <v>741464</v>
       </c>
       <c r="R13" t="n">
-        <v>7294517</v>
+        <v>7294503</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1975,12 +1969,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1995,27 +1994,27 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110044379</t>
+          <t>https://artportalen.se/Sighting/129000536</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129000536</v>
+        <v>135825120</v>
       </c>
       <c r="B14" t="n">
-        <v>93197</v>
+        <v>93347</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2040,24 +2039,20 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>Sv Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>741464</v>
+        <v>741122</v>
       </c>
       <c r="R14" t="n">
-        <v>7294503</v>
+        <v>7294512</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2081,17 +2076,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2106,24 +2106,24 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000536</t>
+          <t>https://artportalen.se/Sighting/135825120</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135825120</v>
+        <v>135825130</v>
       </c>
       <c r="B15" t="n">
         <v>93347</v>
@@ -2158,10 +2158,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>741122</v>
+        <v>741149</v>
       </c>
       <c r="R15" t="n">
-        <v>7294512</v>
+        <v>7294363</v>
       </c>
       <c r="S15" t="n">
         <v>6</v>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2229,13 +2229,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825120</t>
+          <t>https://artportalen.se/Sighting/135825130</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135825130</v>
+        <v>135825132</v>
       </c>
       <c r="B16" t="n">
         <v>93347</v>
@@ -2270,10 +2270,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>741149</v>
+        <v>741186</v>
       </c>
       <c r="R16" t="n">
-        <v>7294363</v>
+        <v>7294441</v>
       </c>
       <c r="S16" t="n">
         <v>6</v>
@@ -2305,7 +2305,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2341,13 +2341,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825130</t>
+          <t>https://artportalen.se/Sighting/135825132</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135825132</v>
+        <v>135828222</v>
       </c>
       <c r="B17" t="n">
         <v>93347</v>
@@ -2376,19 +2376,22 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sv Sikträskberget, Nb</t>
+          <t>SV Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>741186</v>
+        <v>741097</v>
       </c>
       <c r="R17" t="n">
-        <v>7294441</v>
+        <v>7294374</v>
       </c>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2417,7 +2420,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>19:37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2427,7 +2430,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>19:37</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2436,30 +2439,36 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825132</t>
+          <t>https://artportalen.se/Sighting/135828222</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135828222</v>
+        <v>135828226</v>
       </c>
       <c r="B18" t="n">
         <v>93347</v>
@@ -2497,13 +2506,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>741097</v>
+        <v>741113</v>
       </c>
       <c r="R18" t="n">
-        <v>7294374</v>
+        <v>7294382</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2532,7 +2541,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>19:37</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2542,7 +2551,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>19:37</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2574,16 +2583,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135828222</t>
+          <t>https://artportalen.se/Sighting/135828226</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135828226</v>
+        <v>129000539</v>
       </c>
       <c r="B19" t="n">
-        <v>93347</v>
+        <v>93209</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2591,40 +2600,41 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>SV Sikträsket, Nb</t>
+          <t>Grundsel, Nb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>741113</v>
+        <v>741260</v>
       </c>
       <c r="R19" t="n">
-        <v>7294382</v>
+        <v>7294367</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2648,22 +2658,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>19:56</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>19:56</t>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2672,36 +2677,30 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135828226</t>
+          <t>https://artportalen.se/Sighting/129000539</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129000539</v>
+        <v>129000541</v>
       </c>
       <c r="B20" t="n">
         <v>93209</v>
@@ -2740,10 +2739,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>741260</v>
+        <v>741209</v>
       </c>
       <c r="R20" t="n">
-        <v>7294367</v>
+        <v>7294469</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2806,58 +2805,50 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000539</t>
+          <t>https://artportalen.se/Sighting/129000541</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129000541</v>
+        <v>135825125</v>
       </c>
       <c r="B21" t="n">
-        <v>93209</v>
+        <v>93376</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4366</v>
+        <v>5449</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>Sv Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>741209</v>
+        <v>741107</v>
       </c>
       <c r="R21" t="n">
-        <v>7294469</v>
+        <v>7294391</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2881,17 +2872,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>och äldre fruktkropp</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2906,27 +2907,27 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000541</t>
+          <t>https://artportalen.se/Sighting/135825125</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135825125</v>
+        <v>135825123</v>
       </c>
       <c r="B22" t="n">
-        <v>93376</v>
+        <v>91421</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2934,19 +2935,23 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5449</v>
+        <v>5685</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>Pseudomerulius aureus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2954,13 +2959,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>741107</v>
+        <v>741088</v>
       </c>
       <c r="R22" t="n">
         <v>7294391</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2989,7 +2994,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2999,12 +3004,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>19:44</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>och äldre fruktkropp</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3030,54 +3030,58 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825125</t>
+          <t>https://artportalen.se/Sighting/135825123</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135825123</v>
+        <v>129000537</v>
       </c>
       <c r="B23" t="n">
-        <v>91421</v>
+        <v>93235</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5685</v>
+        <v>5966</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sv Sikträskberget, Nb</t>
+          <t>Grundsel, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>741088</v>
+        <v>741430</v>
       </c>
       <c r="R23" t="n">
-        <v>7294391</v>
+        <v>7294484</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3101,22 +3105,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>19:33</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>19:33</t>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3131,69 +3130,65 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825123</t>
+          <t>https://artportalen.se/Sighting/129000537</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129000537</v>
+        <v>131421831</v>
       </c>
       <c r="B24" t="n">
-        <v>93235</v>
+        <v>79373</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>Sarvasvägen, Nb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>741430</v>
+        <v>741264</v>
       </c>
       <c r="R24" t="n">
-        <v>7294484</v>
+        <v>7294336</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3217,17 +3212,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3242,49 +3232,49 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000537</t>
+          <t>https://artportalen.se/Sighting/131421831</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131421831</v>
+        <v>131421828</v>
       </c>
       <c r="B25" t="n">
-        <v>79373</v>
+        <v>79397</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3294,10 +3284,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>741264</v>
+        <v>741410</v>
       </c>
       <c r="R25" t="n">
-        <v>7294336</v>
+        <v>7294501</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3355,16 +3345,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131421831</t>
+          <t>https://artportalen.se/Sighting/131421828</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131421828</v>
+        <v>135828228</v>
       </c>
       <c r="B26" t="n">
-        <v>79397</v>
+        <v>79465</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3390,16 +3380,19 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sarvasvägen, Nb</t>
+          <t>SV Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>741410</v>
+        <v>741122</v>
       </c>
       <c r="R26" t="n">
-        <v>7294501</v>
+        <v>7294378</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3426,12 +3419,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>19:58</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>19:58</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3440,71 +3443,89 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131421828</t>
+          <t>https://artportalen.se/Sighting/135828228</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135828228</v>
+        <v>135825128</v>
       </c>
       <c r="B27" t="n">
-        <v>79465</v>
+        <v>78844</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6434</v>
+        <v>6437</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>SV Sikträsket, Nb</t>
+          <t>Sv Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>741122</v>
+        <v>741118</v>
       </c>
       <c r="R27" t="n">
-        <v>7294378</v>
+        <v>7294382</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3536,7 +3557,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>19:58</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3546,7 +3567,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>19:58</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3555,54 +3576,33 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135828228</t>
+          <t>https://artportalen.se/Sighting/135825128</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135825128</v>
+        <v>129000543</v>
       </c>
       <c r="B28" t="n">
-        <v>78844</v>
+        <v>79084</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3610,37 +3610,41 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Sv Sikträskberget, Nb</t>
+          <t>Grundsel, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>741118</v>
+        <v>741337</v>
       </c>
       <c r="R28" t="n">
-        <v>7294382</v>
+        <v>7294536</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3664,22 +3668,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>19:56</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>19:56</t>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3694,27 +3693,27 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825128</t>
+          <t>https://artportalen.se/Sighting/129000543</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129000543</v>
+        <v>129000542</v>
       </c>
       <c r="B29" t="n">
-        <v>79084</v>
+        <v>79946</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3722,21 +3721,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3750,10 +3749,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>741337</v>
+        <v>741225</v>
       </c>
       <c r="R29" t="n">
-        <v>7294536</v>
+        <v>7294470</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3816,13 +3815,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000543</t>
+          <t>https://artportalen.se/Sighting/129000542</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129000542</v>
+        <v>129000544</v>
       </c>
       <c r="B30" t="n">
         <v>79946</v>
@@ -3861,10 +3860,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>741225</v>
+        <v>741341</v>
       </c>
       <c r="R30" t="n">
-        <v>7294470</v>
+        <v>7294535</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3927,16 +3926,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000542</t>
+          <t>https://artportalen.se/Sighting/129000544</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129000544</v>
+        <v>135825121</v>
       </c>
       <c r="B31" t="n">
-        <v>79946</v>
+        <v>80060</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3961,24 +3960,20 @@
           <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>Sv Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>741341</v>
+        <v>741110</v>
       </c>
       <c r="R31" t="n">
-        <v>7294535</v>
+        <v>7294497</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4002,17 +3997,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4027,27 +4027,27 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000544</t>
+          <t>https://artportalen.se/Sighting/135825121</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135825121</v>
+        <v>135825127</v>
       </c>
       <c r="B32" t="n">
-        <v>80060</v>
+        <v>78445</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4055,21 +4055,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4079,13 +4079,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>741110</v>
+        <v>741118</v>
       </c>
       <c r="R32" t="n">
-        <v>7294497</v>
+        <v>7294382</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4150,16 +4150,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825121</t>
+          <t>https://artportalen.se/Sighting/135825127</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135825127</v>
+        <v>131421821</v>
       </c>
       <c r="B33" t="n">
-        <v>78445</v>
+        <v>57975</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4167,37 +4167,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6487</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Sv Sikträskberget, Nb</t>
+          <t>Sarvasvägen, Nb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>741118</v>
+        <v>741194</v>
       </c>
       <c r="R33" t="n">
-        <v>7294382</v>
+        <v>7294285</v>
       </c>
       <c r="S33" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4221,22 +4221,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>19:55</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>19:55</t>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack färska och gamla, tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4262,13 +4257,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825127</t>
+          <t>https://artportalen.se/Sighting/131421821</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131421821</v>
+        <v>131421823</v>
       </c>
       <c r="B34" t="n">
         <v>57975</v>
@@ -4303,10 +4298,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>741194</v>
+        <v>741167</v>
       </c>
       <c r="R34" t="n">
-        <v>7294285</v>
+        <v>7294289</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4343,7 +4338,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack färska och gamla, tall</t>
+          <t>Nya och gamla ringhack rikligt, tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4369,13 +4364,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131421821</t>
+          <t>https://artportalen.se/Sighting/131421823</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131421823</v>
+        <v>131421824</v>
       </c>
       <c r="B35" t="n">
         <v>57975</v>
@@ -4410,10 +4405,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>741167</v>
+        <v>741275</v>
       </c>
       <c r="R35" t="n">
-        <v>7294289</v>
+        <v>7294333</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4450,7 +4445,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Nya och gamla ringhack rikligt, tall</t>
+          <t>Gamla och nya ringhack, tallhed.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4476,13 +4471,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131421823</t>
+          <t>https://artportalen.se/Sighting/131421824</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131421824</v>
+        <v>131421825</v>
       </c>
       <c r="B36" t="n">
         <v>57975</v>
@@ -4517,10 +4512,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>741275</v>
+        <v>741401</v>
       </c>
       <c r="R36" t="n">
-        <v>7294333</v>
+        <v>7294510</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4557,7 +4552,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Gamla och nya ringhack, tallhed.</t>
+          <t>Nya och gamla ringhack, rikligt, tall.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4583,13 +4578,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131421824</t>
+          <t>https://artportalen.se/Sighting/131421825</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131421825</v>
+        <v>132365365</v>
       </c>
       <c r="B37" t="n">
         <v>57975</v>
@@ -4618,19 +4613,27 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sarvasvägen, Nb</t>
+          <t>Väster om Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>741401</v>
+        <v>741417</v>
       </c>
       <c r="R37" t="n">
-        <v>7294510</v>
+        <v>7294498</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4664,7 +4667,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Nya och gamla ringhack, rikligt, tall.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4679,24 +4682,24 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131421825</t>
+          <t>https://artportalen.se/Sighting/132365365</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132365365</v>
+        <v>132365428</v>
       </c>
       <c r="B38" t="n">
         <v>57975</v>
@@ -4739,10 +4742,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>741417</v>
+        <v>741294</v>
       </c>
       <c r="R38" t="n">
-        <v>7294498</v>
+        <v>7294330</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4779,7 +4782,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Flera ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4805,13 +4808,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132365365</t>
+          <t>https://artportalen.se/Sighting/132365428</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132365428</v>
+        <v>132365494</v>
       </c>
       <c r="B39" t="n">
         <v>57975</v>
@@ -4844,20 +4847,20 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Väster om Sikträsket, Nb</t>
+          <t>SydVäst om Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>741294</v>
+        <v>741247</v>
       </c>
       <c r="R39" t="n">
-        <v>7294330</v>
+        <v>7294318</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4894,14 +4897,14 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Flera ringhack på tall</t>
+          <t>Flertalet ringhack på träd i direkt anslutning till bohålet</t>
         </is>
       </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG39" t="b">
         <v>0</v>
@@ -4920,16 +4923,16 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132365428</t>
+          <t>https://artportalen.se/Sighting/132365494</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132365494</v>
+        <v>135825133</v>
       </c>
       <c r="B40" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4955,27 +4958,19 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>SydVäst om Sikträsket, Nb</t>
+          <t>Sv Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>741247</v>
+        <v>741176</v>
       </c>
       <c r="R40" t="n">
-        <v>7294318</v>
+        <v>7294442</v>
       </c>
       <c r="S40" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4999,24 +4994,34 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>20:17</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>20:17</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Flertalet ringhack på träd i direkt anslutning till bohålet</t>
+          <t>Färska och gamla ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="b">
         <v>0</v>
@@ -5024,24 +5029,24 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132365494</t>
+          <t>https://artportalen.se/Sighting/135825133</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135825133</v>
+        <v>135828227</v>
       </c>
       <c r="B41" t="n">
         <v>57980</v>
@@ -5070,16 +5075,24 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sv Sikträskberget, Nb</t>
+          <t>SV Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>741176</v>
+        <v>741122</v>
       </c>
       <c r="R41" t="n">
-        <v>7294442</v>
+        <v>7294378</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5111,7 +5124,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>20:17</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5121,12 +5134,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>20:17</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Färska och gamla ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5137,28 +5150,48 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825133</t>
+          <t>https://artportalen.se/Sighting/135828227</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135828227</v>
+        <v>135828230</v>
       </c>
       <c r="B42" t="n">
         <v>57980</v>
@@ -5191,7 +5224,7 @@
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -5201,10 +5234,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>741122</v>
+        <v>741155</v>
       </c>
       <c r="R42" t="n">
-        <v>7294378</v>
+        <v>7294379</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5236,7 +5269,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>19:58</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5246,12 +5279,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>19:58</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5297,13 +5330,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135828227</t>
+          <t>https://artportalen.se/Sighting/135828230</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135828230</v>
+        <v>135828231</v>
       </c>
       <c r="B43" t="n">
         <v>57980</v>
@@ -5336,7 +5369,7 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -5346,13 +5379,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>741155</v>
+        <v>741186</v>
       </c>
       <c r="R43" t="n">
-        <v>7294379</v>
+        <v>7294423</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5381,7 +5414,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5391,12 +5424,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5411,21 +5444,6 @@
       <c r="AH43" t="inlineStr">
         <is>
           <t>Sandtallskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5442,59 +5460,56 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135828230</t>
+          <t>https://artportalen.se/Sighting/135828231</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135828231</v>
+        <v>135825126</v>
       </c>
       <c r="B44" t="n">
-        <v>57980</v>
+        <v>57167</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>SV Sikträsket, Nb</t>
+          <t>Sv Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>741186</v>
+        <v>741114</v>
       </c>
       <c r="R44" t="n">
-        <v>7294423</v>
+        <v>7294391</v>
       </c>
       <c r="S44" t="n">
         <v>6</v>
@@ -5526,7 +5541,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5536,12 +5551,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>20:11</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5552,79 +5562,77 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135828231</t>
+          <t>https://artportalen.se/Sighting/135825126</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135825126</v>
+        <v>135857317</v>
       </c>
       <c r="B45" t="n">
-        <v>57167</v>
+        <v>58141</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sv Sikträskberget, Nb</t>
+          <t>SV Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>741114</v>
+        <v>741177</v>
       </c>
       <c r="R45" t="n">
-        <v>7294391</v>
+        <v>7294392</v>
       </c>
       <c r="S45" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5653,7 +5661,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5663,7 +5671,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>20:09</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Lockläten</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5674,74 +5687,71 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825126</t>
+          <t>https://artportalen.se/Sighting/135857317</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135857317</v>
+        <v>131421826</v>
       </c>
       <c r="B46" t="n">
-        <v>58141</v>
+        <v>58131</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>103023</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>SV Sikträsket, Nb</t>
+          <t>Sarvasvägen, Nb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>741177</v>
+        <v>741150</v>
       </c>
       <c r="R46" t="n">
-        <v>7294392</v>
+        <v>7294265</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5768,27 +5778,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>20:09</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>20:09</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Lockläten</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5799,33 +5794,28 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135857317</t>
+          <t>https://artportalen.se/Sighting/131421826</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131421826</v>
+        <v>132365028</v>
       </c>
       <c r="B47" t="n">
         <v>58131</v>
@@ -5853,20 +5843,36 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sarvasvägen, Nb</t>
+          <t>SydVäst om Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>741150</v>
+        <v>741151</v>
       </c>
       <c r="R47" t="n">
-        <v>7294265</v>
+        <v>7294262</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5893,9 +5899,19 @@
           <t>2026-03-01</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5910,44 +5926,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131421826</t>
+          <t>https://artportalen.se/Sighting/132365028</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132365028</v>
+        <v>110044410</v>
       </c>
       <c r="B48" t="n">
-        <v>58131</v>
+        <v>58057</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103023</v>
+        <v>103031</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5955,33 +5971,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>SydVäst om Sikträsket, Nb</t>
+          <t>Rävabacken Utv, Nb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>741151</v>
+        <v>741267</v>
       </c>
       <c r="R48" t="n">
-        <v>7294262</v>
+        <v>7294536</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6008,22 +6008,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>13:02</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>13:02</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6038,65 +6028,69 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132365028</t>
+          <t>https://artportalen.se/Sighting/110044410</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>110044410</v>
+        <v>135828221</v>
       </c>
       <c r="B49" t="n">
-        <v>58057</v>
+        <v>98138</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103031</v>
+        <v>221945</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Rävabacken Utv, Nb</t>
+          <t>SV Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>741267</v>
+        <v>741098</v>
       </c>
       <c r="R49" t="n">
-        <v>7294536</v>
+        <v>7294366</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6120,12 +6114,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6134,75 +6138,81 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110044410</t>
+          <t>https://artportalen.se/Sighting/135828221</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135828221</v>
+        <v>129000540</v>
       </c>
       <c r="B50" t="n">
-        <v>98138</v>
+        <v>79085</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221945</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>SV Sikträsket, Nb</t>
+          <t>Grundsel, Nb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>741098</v>
+        <v>741238</v>
       </c>
       <c r="R50" t="n">
-        <v>7294366</v>
+        <v>7294334</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6226,22 +6236,17 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>19:35</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>19:35</t>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6250,39 +6255,33 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135828221</t>
+          <t>https://artportalen.se/Sighting/129000540</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129000540</v>
+        <v>135828224</v>
       </c>
       <c r="B51" t="n">
-        <v>79085</v>
+        <v>79199</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6307,24 +6306,23 @@
           <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>SV Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>741238</v>
+        <v>741114</v>
       </c>
       <c r="R51" t="n">
-        <v>7294334</v>
+        <v>7294379</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6348,17 +6346,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6367,33 +6370,39 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000540</t>
+          <t>https://artportalen.se/Sighting/135828224</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135828224</v>
+        <v>135825134</v>
       </c>
       <c r="B52" t="n">
-        <v>79199</v>
+        <v>79464</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6401,40 +6410,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>260591</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>SV Sikträsket, Nb</t>
+          <t>Sv Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>741114</v>
+        <v>741168</v>
       </c>
       <c r="R52" t="n">
-        <v>7294379</v>
+        <v>7294460</v>
       </c>
       <c r="S52" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6463,7 +6469,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6473,7 +6479,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6482,140 +6488,22 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135828224</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>135825134</v>
-      </c>
-      <c r="B53" t="n">
-        <v>79464</v>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E53" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>Sv Sikträskberget, Nb</t>
-        </is>
-      </c>
-      <c r="Q53" t="n">
-        <v>741168</v>
-      </c>
-      <c r="R53" t="n">
-        <v>7294460</v>
-      </c>
-      <c r="S53" t="n">
-        <v>5</v>
-      </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>Älvsbyn</t>
-        </is>
-      </c>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W53" t="inlineStr">
-        <is>
-          <t>Älvsby</t>
-        </is>
-      </c>
-      <c r="Y53" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>20:20</t>
-        </is>
-      </c>
-      <c r="AA53" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>20:20</t>
-        </is>
-      </c>
-      <c r="AD53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT53" t="inlineStr"/>
-      <c r="AW53" t="inlineStr">
-        <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr"/>
-      <c r="AZ53" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135825134</t>
         </is>
@@ -6674,7 +6562,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51047-2025 artfynd.xlsx
+++ b/artfynd/A 51047-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135825129</v>
       </c>
       <c r="B2" t="n">
-        <v>83420</v>
+        <v>83422</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>135825124</v>
       </c>
       <c r="B3" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>135828232</v>
       </c>
       <c r="B5" t="n">
-        <v>89329</v>
+        <v>89331</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>135828223</v>
       </c>
       <c r="B6" t="n">
-        <v>87458</v>
+        <v>87460</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>135825131</v>
       </c>
       <c r="B8" t="n">
-        <v>93339</v>
+        <v>93354</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>135825120</v>
       </c>
       <c r="B14" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>135825130</v>
       </c>
       <c r="B15" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>135825132</v>
       </c>
       <c r="B16" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2350,7 +2350,7 @@
         <v>135828222</v>
       </c>
       <c r="B17" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>135828226</v>
       </c>
       <c r="B18" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>135825125</v>
       </c>
       <c r="B21" t="n">
-        <v>93376</v>
+        <v>93391</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>135825123</v>
       </c>
       <c r="B22" t="n">
-        <v>91421</v>
+        <v>91423</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>135828228</v>
       </c>
       <c r="B26" t="n">
-        <v>79465</v>
+        <v>79467</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>135825128</v>
       </c>
       <c r="B27" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>135825121</v>
       </c>
       <c r="B31" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>135825127</v>
       </c>
       <c r="B32" t="n">
-        <v>78445</v>
+        <v>78447</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>135825133</v>
       </c>
       <c r="B40" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>135828227</v>
       </c>
       <c r="B41" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>135828230</v>
       </c>
       <c r="B42" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>135828231</v>
       </c>
       <c r="B43" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         <v>135825126</v>
       </c>
       <c r="B44" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5586,7 +5586,7 @@
         <v>135857317</v>
       </c>
       <c r="B45" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
         <v>135828221</v>
       </c>
       <c r="B49" t="n">
-        <v>98138</v>
+        <v>98155</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
         <v>135828224</v>
       </c>
       <c r="B51" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>135825134</v>
       </c>
       <c r="B52" t="n">
-        <v>79464</v>
+        <v>79466</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 51047-2025 artfynd.xlsx
+++ b/artfynd/A 51047-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135825129</v>
       </c>
       <c r="B2" t="n">
-        <v>83422</v>
+        <v>83423</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>135825124</v>
       </c>
       <c r="B3" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>135828232</v>
       </c>
       <c r="B5" t="n">
-        <v>89331</v>
+        <v>89332</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>135828223</v>
       </c>
       <c r="B6" t="n">
-        <v>87460</v>
+        <v>87461</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>135825131</v>
       </c>
       <c r="B8" t="n">
-        <v>93354</v>
+        <v>93355</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>135825120</v>
       </c>
       <c r="B14" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>135825130</v>
       </c>
       <c r="B15" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>135825132</v>
       </c>
       <c r="B16" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2350,7 +2350,7 @@
         <v>135828222</v>
       </c>
       <c r="B17" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>135828226</v>
       </c>
       <c r="B18" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>135825125</v>
       </c>
       <c r="B21" t="n">
-        <v>93391</v>
+        <v>93392</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>135825123</v>
       </c>
       <c r="B22" t="n">
-        <v>91423</v>
+        <v>91424</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>135828228</v>
       </c>
       <c r="B26" t="n">
-        <v>79467</v>
+        <v>79468</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>135825128</v>
       </c>
       <c r="B27" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>135825121</v>
       </c>
       <c r="B31" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>135825127</v>
       </c>
       <c r="B32" t="n">
-        <v>78447</v>
+        <v>78448</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
         <v>135828221</v>
       </c>
       <c r="B49" t="n">
-        <v>98155</v>
+        <v>98156</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
         <v>135828224</v>
       </c>
       <c r="B51" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>135825134</v>
       </c>
       <c r="B52" t="n">
-        <v>79466</v>
+        <v>79467</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 51047-2025 artfynd.xlsx
+++ b/artfynd/A 51047-2025 artfynd.xlsx
@@ -1014,7 +1014,7 @@
         <v>135828232</v>
       </c>
       <c r="B5" t="n">
-        <v>89332</v>
+        <v>89333</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>135828223</v>
       </c>
       <c r="B6" t="n">
-        <v>87461</v>
+        <v>87462</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>135825131</v>
       </c>
       <c r="B8" t="n">
-        <v>93355</v>
+        <v>93356</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>135825120</v>
       </c>
       <c r="B14" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>135825130</v>
       </c>
       <c r="B15" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>135825132</v>
       </c>
       <c r="B16" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2350,7 +2350,7 @@
         <v>135828222</v>
       </c>
       <c r="B17" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>135828226</v>
       </c>
       <c r="B18" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>135825125</v>
       </c>
       <c r="B21" t="n">
-        <v>93392</v>
+        <v>93393</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>135825123</v>
       </c>
       <c r="B22" t="n">
-        <v>91424</v>
+        <v>91425</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
         <v>135828221</v>
       </c>
       <c r="B49" t="n">
-        <v>98156</v>
+        <v>98157</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 51047-2025 artfynd.xlsx
+++ b/artfynd/A 51047-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135825129</v>
       </c>
       <c r="B2" t="n">
-        <v>83423</v>
+        <v>83424</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>135825124</v>
       </c>
       <c r="B3" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>135828232</v>
       </c>
       <c r="B5" t="n">
-        <v>89333</v>
+        <v>89334</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>135828223</v>
       </c>
       <c r="B6" t="n">
-        <v>87462</v>
+        <v>87463</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>135825131</v>
       </c>
       <c r="B8" t="n">
-        <v>93356</v>
+        <v>93357</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>135825120</v>
       </c>
       <c r="B14" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>135825130</v>
       </c>
       <c r="B15" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>135825132</v>
       </c>
       <c r="B16" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2350,7 +2350,7 @@
         <v>135828222</v>
       </c>
       <c r="B17" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>135828226</v>
       </c>
       <c r="B18" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>135825125</v>
       </c>
       <c r="B21" t="n">
-        <v>93393</v>
+        <v>93394</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>135825123</v>
       </c>
       <c r="B22" t="n">
-        <v>91425</v>
+        <v>91426</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>135828228</v>
       </c>
       <c r="B26" t="n">
-        <v>79468</v>
+        <v>79469</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>135825128</v>
       </c>
       <c r="B27" t="n">
-        <v>78847</v>
+        <v>78848</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>135825121</v>
       </c>
       <c r="B31" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>135825127</v>
       </c>
       <c r="B32" t="n">
-        <v>78448</v>
+        <v>78449</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>135825133</v>
       </c>
       <c r="B40" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>135828227</v>
       </c>
       <c r="B41" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>135828230</v>
       </c>
       <c r="B42" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>135828231</v>
       </c>
       <c r="B43" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         <v>135825126</v>
       </c>
       <c r="B44" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5586,7 +5586,7 @@
         <v>135857317</v>
       </c>
       <c r="B45" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
         <v>135828221</v>
       </c>
       <c r="B49" t="n">
-        <v>98157</v>
+        <v>98158</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
         <v>135828224</v>
       </c>
       <c r="B51" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>135825134</v>
       </c>
       <c r="B52" t="n">
-        <v>79467</v>
+        <v>79468</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 51047-2025 artfynd.xlsx
+++ b/artfynd/A 51047-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135825129</v>
       </c>
       <c r="B2" t="n">
-        <v>83424</v>
+        <v>83428</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>135825124</v>
       </c>
       <c r="B3" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>135828232</v>
       </c>
       <c r="B5" t="n">
-        <v>89334</v>
+        <v>89340</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>135828223</v>
       </c>
       <c r="B6" t="n">
-        <v>87463</v>
+        <v>87469</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>135825131</v>
       </c>
       <c r="B8" t="n">
-        <v>93357</v>
+        <v>93363</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>135825120</v>
       </c>
       <c r="B14" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>135825130</v>
       </c>
       <c r="B15" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>135825132</v>
       </c>
       <c r="B16" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2350,7 +2350,7 @@
         <v>135828222</v>
       </c>
       <c r="B17" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>135828226</v>
       </c>
       <c r="B18" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>135825125</v>
       </c>
       <c r="B21" t="n">
-        <v>93394</v>
+        <v>93400</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>135825123</v>
       </c>
       <c r="B22" t="n">
-        <v>91426</v>
+        <v>91432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>135828228</v>
       </c>
       <c r="B26" t="n">
-        <v>79469</v>
+        <v>79473</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>135825128</v>
       </c>
       <c r="B27" t="n">
-        <v>78848</v>
+        <v>78852</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>135825121</v>
       </c>
       <c r="B31" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>135825127</v>
       </c>
       <c r="B32" t="n">
-        <v>78449</v>
+        <v>78453</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>135825133</v>
       </c>
       <c r="B40" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>135828227</v>
       </c>
       <c r="B41" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>135828230</v>
       </c>
       <c r="B42" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>135828231</v>
       </c>
       <c r="B43" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         <v>135825126</v>
       </c>
       <c r="B44" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5586,7 +5586,7 @@
         <v>135857317</v>
       </c>
       <c r="B45" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
         <v>135828221</v>
       </c>
       <c r="B49" t="n">
-        <v>98158</v>
+        <v>98164</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
         <v>135828224</v>
       </c>
       <c r="B51" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>135825134</v>
       </c>
       <c r="B52" t="n">
-        <v>79468</v>
+        <v>79472</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 51047-2025 artfynd.xlsx
+++ b/artfynd/A 51047-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135825129</v>
       </c>
       <c r="B2" t="n">
-        <v>83428</v>
+        <v>83429</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>135825124</v>
       </c>
       <c r="B3" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>135828232</v>
       </c>
       <c r="B5" t="n">
-        <v>89340</v>
+        <v>89341</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>135828223</v>
       </c>
       <c r="B6" t="n">
-        <v>87469</v>
+        <v>87470</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>135825131</v>
       </c>
       <c r="B8" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>135825120</v>
       </c>
       <c r="B14" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>135825130</v>
       </c>
       <c r="B15" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>135825132</v>
       </c>
       <c r="B16" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2350,7 +2350,7 @@
         <v>135828222</v>
       </c>
       <c r="B17" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>135828226</v>
       </c>
       <c r="B18" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>135825125</v>
       </c>
       <c r="B21" t="n">
-        <v>93400</v>
+        <v>93401</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>135825123</v>
       </c>
       <c r="B22" t="n">
-        <v>91432</v>
+        <v>91433</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>135828228</v>
       </c>
       <c r="B26" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>135825128</v>
       </c>
       <c r="B27" t="n">
-        <v>78852</v>
+        <v>78853</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>135825121</v>
       </c>
       <c r="B31" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>135825127</v>
       </c>
       <c r="B32" t="n">
-        <v>78453</v>
+        <v>78454</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>135825133</v>
       </c>
       <c r="B40" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>135828227</v>
       </c>
       <c r="B41" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>135828230</v>
       </c>
       <c r="B42" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>135828231</v>
       </c>
       <c r="B43" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         <v>135825126</v>
       </c>
       <c r="B44" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5586,7 +5586,7 @@
         <v>135857317</v>
       </c>
       <c r="B45" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
         <v>135828221</v>
       </c>
       <c r="B49" t="n">
-        <v>98164</v>
+        <v>98165</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
         <v>135828224</v>
       </c>
       <c r="B51" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>135825134</v>
       </c>
       <c r="B52" t="n">
-        <v>79472</v>
+        <v>79473</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
